--- a/survey_templates/033_favorite_poster_voting--survey_templates.xlsx
+++ b/survey_templates/033_favorite_poster_voting--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Favorite Poster</t>
+          <t>1. What is your favorite poster?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,17 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poster Name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>The name of your favorite poster</t>
-        </is>
-      </c>
+          <t>2. Why do you like this poster?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -575,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poster URL</t>
+          <t>3. What is the name of your favorite poster?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -598,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Why do you like this poster?</t>
+          <t>4. What is the URL of your favorite poster?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Favorite Poster</t>
+          <t>5. What is the name of the submitters?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>6. What is the email of the submitters?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -667,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>7. What is the phone number of the submitters?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -690,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>8. What is the date of submission?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -713,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>9. What is the time of submission?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Favorite Poster</t>
+          <t>10. What is the url of the submitters?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Why do you like this poster?</t>
+          <t>11. Submitter's information will be displayed publicly on our website?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -782,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>12. Additional comments?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -805,20 +801,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Favorite Poster Name</t>
+          <t>13. Additional comments?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -828,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Favorite Poster URL</t>
+          <t>14. Additional comments?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Why do you like this poster?</t>
+          <t>15. Additional comments?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -874,14 +870,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submission Tracking</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Track your submissions on our website</t>
-        </is>
-      </c>
+          <t>16. Additional comments?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -891,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -901,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submission Tracking Code</t>
+          <t>17. Additional comments?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -914,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -924,590 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submitter Information</t>
+          <t>18. Additional comments?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_nineteen</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submitter Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_twenty</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submitter Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>pagetwentyone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_twentwo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_twenthree</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submitter Name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_twentfour</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_twentyfive</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submitter URL</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>page_twentysix</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Submitter Info</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Submitter information will be displayed publicly on our website</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>page_twentyseven</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Submitter Phone Number</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>page_twentyeight</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Submitter Email</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>page_twentynine</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Submitter URL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>page_thirty</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Submitter Information</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>page_thirtyone</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Submitter Date</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>page_thirtytwo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Submitter Time</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>page_thirtythree</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Submitter Notes</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>page_thirtyfour</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Submitter Name</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>page_thirtyfive</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Submitter URL</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>page_thirtysix</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Submitter Info</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>page_thirtyseven</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Submitter Phone</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>page_thirtyeight</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Submitter Email</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>page_thirtynine</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Submitter Date</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>pageforty</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Submitter Time</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>pagefortyeen</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Submitter URL</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>pagefortyone</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Submitter Information</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>pagefortytwo</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Submitter Notes</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1524,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1597,108 +1010,6 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Poster 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>page_five_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>page_five_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>page_five_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>page_ten_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>page_ten_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>page_ten_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Option 3</t>
         </is>
       </c>
     </row>
